--- a/app/content/diaolan.xlsx
+++ b/app/content/diaolan.xlsx
@@ -882,7 +882,7 @@
         <v>雷霆手段</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D2" t="str">
         <v>禁军封锁九门，先斩后奏。</v>
@@ -905,7 +905,7 @@
         <v>步步为营</v>
       </c>
       <c r="C3" t="str">
-        <v>理</v>
+        <v>器</v>
       </c>
       <c r="D3" t="str">
         <v>先夺禁军印信，再断其耳目。</v>
@@ -928,7 +928,7 @@
         <v>按兵不动</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>隐</v>
       </c>
       <c r="D4" t="str">
         <v>示弱于外，等待时机。</v>
@@ -951,7 +951,7 @@
         <v>施恩旧部</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>器</v>
       </c>
       <c r="D5" t="str">
         <v>多年布下的人情，今夜一并兑现。</v>
@@ -974,7 +974,7 @@
         <v>以身作饵</v>
       </c>
       <c r="C6" t="str">
-        <v>威</v>
+        <v>策</v>
       </c>
       <c r="D6" t="str">
         <v>亲赴军营，以天子之身压阵。</v>
@@ -997,7 +997,7 @@
         <v>断腕求生</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>弃车保帅，先活着退出长安。</v>
